--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>182200</v>
+      </c>
+      <c r="E8" s="3">
         <v>160300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>213000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>153000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2900</v>
       </c>
       <c r="I8" s="3">
         <v>2900</v>
       </c>
       <c r="J8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E9" s="3">
         <v>157000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>208000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>148200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,37 +884,43 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -905,10 +928,10 @@
         <v>500</v>
       </c>
       <c r="E15" s="3">
+        <v>500</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
@@ -920,13 +943,16 @@
         <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>185800</v>
+      </c>
+      <c r="E17" s="3">
         <v>160300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>213900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>155400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1800</v>
       </c>
       <c r="H18" s="3">
         <v>-1800</v>
       </c>
       <c r="I18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,124 +1039,137 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E21" s="3">
         <v>600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1197,11 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,138 +1678,153 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E43" s="3">
         <v>47500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>300</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
       </c>
       <c r="H44" s="3">
+        <v>300</v>
+      </c>
+      <c r="I44" s="3">
         <v>200</v>
-      </c>
-      <c r="I44" s="3">
-        <v>300</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>300</v>
+      </c>
+      <c r="L44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E46" s="3">
         <v>53200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>8800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4900</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -1727,72 +1832,81 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>4600</v>
       </c>
       <c r="I48" s="3">
         <v>4600</v>
       </c>
       <c r="J48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K48" s="3">
         <v>2300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E49" s="3">
         <v>6600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,8 +1966,11 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1864,7 +1984,7 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
@@ -1878,8 +1998,11 @@
       <c r="K52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E54" s="3">
         <v>72300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,22 +2092,23 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E57" s="3">
         <v>40500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1000</v>
       </c>
       <c r="H57" s="3">
         <v>1000</v>
@@ -1986,21 +2117,24 @@
         <v>1000</v>
       </c>
       <c r="J57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -2009,7 +2143,7 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>300</v>
@@ -2020,77 +2154,86 @@
       <c r="K58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E60" s="3">
         <v>45500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>700</v>
       </c>
       <c r="F61" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G61" s="3">
         <v>800</v>
@@ -2099,27 +2242,30 @@
         <v>800</v>
       </c>
       <c r="I61" s="3">
+        <v>800</v>
+      </c>
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="E62" s="3">
         <v>3000</v>
       </c>
       <c r="F62" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="G62" s="3">
         <v>3300</v>
@@ -2128,16 +2274,19 @@
         <v>3300</v>
       </c>
       <c r="I62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J62" s="3">
         <v>3400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1100</v>
       </c>
       <c r="K62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E66" s="3">
         <v>49200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-80200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-80400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-79400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-77000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-75100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-73300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-71400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E76" s="3">
         <v>23200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +2829,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2640,10 +2839,10 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
@@ -2654,14 +2853,17 @@
       <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
+      <c r="J83" s="3">
+        <v>500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-12200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3209,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3239,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,19 +3335,22 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
@@ -3113,16 +3359,19 @@
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3399,39 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1800</v>
       </c>
       <c r="G102" s="3">
         <v>-1800</v>
       </c>
       <c r="H102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="K102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,161 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>171200</v>
+      </c>
+      <c r="F8" s="3">
         <v>182200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>160300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>213000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>153000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>172000</v>
+      </c>
+      <c r="F9" s="3">
         <v>179300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>157000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>208000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>148200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3100</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +848,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +882,14 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,57 +920,69 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1300</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-500</v>
+        <v>1600</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -946,13 +991,19 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
+        <v>500</v>
+      </c>
+      <c r="L15" s="3">
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,40 +1013,48 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>185800</v>
+        <v>111500</v>
       </c>
       <c r="E17" s="3">
-        <v>160300</v>
+        <v>175000</v>
       </c>
       <c r="F17" s="3">
-        <v>213900</v>
+        <v>186100</v>
       </c>
       <c r="G17" s="3">
+        <v>160700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>214500</v>
+      </c>
+      <c r="I17" s="3">
         <v>155400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1003,31 +1062,37 @@
         <v>-3600</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-3800</v>
       </c>
       <c r="F18" s="3">
-        <v>-900</v>
+        <v>-3900</v>
       </c>
       <c r="G18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,72 +1105,86 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1700</v>
+        <v>3300</v>
       </c>
       <c r="E20" s="3">
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="F20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1300</v>
       </c>
       <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1133,43 +1212,55 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1800</v>
       </c>
       <c r="J23" s="3">
         <v>-1900</v>
       </c>
       <c r="K23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1291,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1329,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1800</v>
       </c>
       <c r="J26" s="3">
         <v>-1900</v>
       </c>
       <c r="K26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1800</v>
       </c>
       <c r="J27" s="3">
         <v>-1900</v>
       </c>
       <c r="K27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1443,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1481,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1519,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1557,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1700</v>
+        <v>-3300</v>
       </c>
       <c r="E32" s="3">
-        <v>-200</v>
+        <v>-1900</v>
       </c>
       <c r="F32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1800</v>
       </c>
       <c r="J33" s="3">
         <v>-1900</v>
       </c>
       <c r="K33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1671,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1800</v>
       </c>
       <c r="J35" s="3">
         <v>-1900</v>
       </c>
       <c r="K35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1772,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1788,48 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>14800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>15800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,232 +1860,280 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100300</v>
+      </c>
+      <c r="F43" s="3">
         <v>61200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>47500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>300</v>
-      </c>
-      <c r="F44" s="3">
-        <v>35100</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
       </c>
       <c r="H44" s="3">
+        <v>35100</v>
+      </c>
+      <c r="I44" s="3">
         <v>300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>200</v>
+      </c>
+      <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
+        <v>300</v>
+      </c>
+      <c r="N44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F45" s="3">
         <v>7000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
       </c>
       <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>112900</v>
+      </c>
+      <c r="F46" s="3">
         <v>70900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>53200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>46700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>18000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="E47" s="3">
+        <v>46400</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>8800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>4900</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F48" s="3">
         <v>15000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F49" s="3">
         <v>4800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2164,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,13 +2202,19 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>100</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -1987,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
@@ -2001,8 +2240,14 @@
       <c r="L52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2278,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>150500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>178100</v>
+      </c>
+      <c r="F54" s="3">
         <v>90700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>72300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>62600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>27200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>25400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2336,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,63 +2352,71 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>48800</v>
+      </c>
+      <c r="F57" s="3">
         <v>57000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>40500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>35500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1000</v>
       </c>
       <c r="J57" s="3">
         <v>1000</v>
       </c>
       <c r="K57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
@@ -2157,136 +2424,166 @@
       <c r="L58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>300</v>
+      </c>
+      <c r="N58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>104600</v>
+      </c>
+      <c r="F60" s="3">
         <v>61900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>45500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>40300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>600</v>
+      </c>
+      <c r="G61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
-      </c>
-      <c r="G61" s="3">
-        <v>800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>800</v>
       </c>
       <c r="I61" s="3">
         <v>800</v>
       </c>
       <c r="J61" s="3">
+        <v>800</v>
+      </c>
+      <c r="K61" s="3">
+        <v>800</v>
+      </c>
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>48600</v>
+      </c>
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3300</v>
       </c>
       <c r="I62" s="3">
         <v>3300</v>
       </c>
       <c r="J62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L62" s="3">
         <v>3400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2614,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2652,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2690,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>157300</v>
+      </c>
+      <c r="F66" s="3">
         <v>68900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>49200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>44000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2748,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2782,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2820,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2858,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2896,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-87400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-87200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-85400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-80200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-80400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-79400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-77000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-75100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-73300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-71400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2972,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3010,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,8 +3048,14 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -2692,31 +3063,37 @@
         <v>21800</v>
       </c>
       <c r="E76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>21800</v>
+      </c>
+      <c r="G76" s="3">
         <v>23200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>24400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3124,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1800</v>
       </c>
       <c r="J81" s="3">
         <v>-1900</v>
       </c>
       <c r="K81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,25 +3225,27 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -2856,14 +3253,20 @@
       <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="K83" s="3">
+        <v>500</v>
+      </c>
+      <c r="L83" s="3">
+        <v>500</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3297,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3335,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3373,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3411,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3449,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,31 +3507,33 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
@@ -3100,8 +3541,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3579,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3617,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>200</v>
+      </c>
+      <c r="F94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4900</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
+      <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3675,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3709,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3747,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3785,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3823,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1400</v>
+        <v>-2800</v>
       </c>
       <c r="E100" s="3">
         <v>3500</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>3500</v>
       </c>
       <c r="H100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3899,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="M102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E8" s="3">
         <v>107900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>171200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>182200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>160300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>213000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>153000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2900</v>
       </c>
       <c r="L8" s="3">
         <v>2900</v>
       </c>
       <c r="M8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N8" s="3">
         <v>3000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E9" s="3">
         <v>108300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>172000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>179300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>157000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>208000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>148200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3100</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,66 +943,72 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
       </c>
       <c r="H15" s="3">
+        <v>500</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -997,13 +1020,16 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E17" s="3">
         <v>111500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>175000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>186100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>160700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>214500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>155400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1800</v>
       </c>
       <c r="K18" s="3">
         <v>-1800</v>
       </c>
       <c r="L18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,84 +1140,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1218,49 +1258,55 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,183 +1956,198 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E43" s="3">
         <v>70300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>300</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>300</v>
+      </c>
+      <c r="L44" s="3">
         <v>200</v>
-      </c>
-      <c r="L44" s="3">
-        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
       <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E45" s="3">
         <v>18300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E46" s="3">
         <v>92200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>112900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>53200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>46300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46400</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>8800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4900</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2050,14 +2155,17 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2065,37 +2173,40 @@
         <v>12000</v>
       </c>
       <c r="E48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F48" s="3">
         <v>14200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>4600</v>
       </c>
       <c r="L48" s="3">
         <v>4600</v>
       </c>
       <c r="M48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N48" s="3">
         <v>2300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2103,37 +2214,40 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>4600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,16 +2325,19 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2232,7 +2352,7 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -2246,8 +2366,11 @@
       <c r="N52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E54" s="3">
         <v>150500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,31 +2484,32 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E57" s="3">
         <v>22500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1000</v>
       </c>
       <c r="K57" s="3">
         <v>1000</v>
@@ -2387,30 +2518,33 @@
         <v>1000</v>
       </c>
       <c r="M57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
@@ -2419,7 +2553,7 @@
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
@@ -2430,84 +2564,93 @@
       <c r="N58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E59" s="3">
         <v>52900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>137600</v>
+      </c>
+      <c r="E60" s="3">
         <v>79000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>104600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2515,19 +2658,19 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
         <v>700</v>
       </c>
       <c r="I61" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J61" s="3">
         <v>800</v>
@@ -2536,36 +2679,39 @@
         <v>800</v>
       </c>
       <c r="L61" s="3">
+        <v>800</v>
+      </c>
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>46300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3000</v>
       </c>
       <c r="H62" s="3">
         <v>3000</v>
       </c>
       <c r="I62" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="J62" s="3">
         <v>3300</v>
@@ -2574,16 +2720,19 @@
         <v>3300</v>
       </c>
       <c r="L62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M62" s="3">
         <v>3400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1100</v>
       </c>
       <c r="N62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E66" s="3">
         <v>128700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>157300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>68900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>49200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-87400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-87200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-85400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-80200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-80400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-77000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-75100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-73300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E76" s="3">
         <v>21800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,28 +3425,29 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
       </c>
       <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
         <v>600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -3259,14 +3458,17 @@
       <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
+      <c r="M83" s="3">
+        <v>500</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3729,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,37 +3739,40 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,28 +4072,31 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
@@ -3859,16 +4105,19 @@
         <v>-100</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1800</v>
       </c>
       <c r="J102" s="3">
         <v>-1800</v>
       </c>
       <c r="K102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N102" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,158 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E8" s="3">
         <v>175000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>107900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>171200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>182200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>213000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>153000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2900</v>
       </c>
       <c r="M8" s="3">
         <v>2900</v>
       </c>
       <c r="N8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O8" s="3">
         <v>3000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>199300</v>
+      </c>
+      <c r="E9" s="3">
         <v>172500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>108300</v>
       </c>
-      <c r="F9" s="3">
-        <v>172000</v>
-      </c>
       <c r="G9" s="3">
+        <v>170700</v>
+      </c>
+      <c r="H9" s="3">
         <v>179300</v>
       </c>
-      <c r="H9" s="3">
-        <v>157000</v>
-      </c>
       <c r="I9" s="3">
-        <v>208000</v>
+        <v>157200</v>
       </c>
       <c r="J9" s="3">
+        <v>208300</v>
+      </c>
+      <c r="K9" s="3">
         <v>148200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3100</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -815,40 +825,43 @@
         <v>2500</v>
       </c>
       <c r="E10" s="3">
-        <v>-400</v>
+        <v>2500</v>
       </c>
       <c r="F10" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
         <v>2900</v>
       </c>
-      <c r="H10" s="3">
-        <v>3300</v>
-      </c>
       <c r="I10" s="3">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="J10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K10" s="3">
         <v>4800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,72 +963,78 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>-500</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1023,13 +1046,16 @@
         <v>500</v>
       </c>
       <c r="N15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E17" s="3">
         <v>177000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>111500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>175000</v>
       </c>
-      <c r="G17" s="3">
-        <v>186100</v>
-      </c>
       <c r="H17" s="3">
+        <v>184400</v>
+      </c>
+      <c r="I17" s="3">
         <v>160700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>214500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>155400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2000</v>
+        <v>-3600</v>
       </c>
       <c r="E18" s="3">
-        <v>-3600</v>
+        <v>-1900</v>
       </c>
       <c r="F18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H18" s="3">
-        <v>-400</v>
+        <v>-2300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1800</v>
       </c>
       <c r="L18" s="3">
         <v>-1800</v>
       </c>
       <c r="M18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,113 +1174,120 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4300</v>
+        <v>-6400</v>
       </c>
       <c r="E20" s="3">
-        <v>3300</v>
+        <v>-3700</v>
       </c>
       <c r="F20" s="3">
-        <v>1900</v>
+        <v>-3700</v>
       </c>
       <c r="G20" s="3">
-        <v>-1400</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>-500</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F21" s="3">
-        <v>-1600</v>
+        <v>500</v>
       </c>
       <c r="G21" s="3">
-        <v>-4800</v>
+        <v>-1500</v>
       </c>
       <c r="H21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I21" s="3">
         <v>600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1261,52 +1301,58 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5300</v>
-      </c>
       <c r="H27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4300</v>
+        <v>6400</v>
       </c>
       <c r="E32" s="3">
-        <v>-3300</v>
+        <v>3700</v>
       </c>
       <c r="F32" s="3">
-        <v>-1900</v>
+        <v>3700</v>
       </c>
       <c r="G32" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-600</v>
+        <v>-1100</v>
       </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>500</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5300</v>
-      </c>
       <c r="H33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5300</v>
-      </c>
       <c r="H35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,213 +2049,231 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E43" s="3">
         <v>118500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>35100</v>
-      </c>
-      <c r="J44" s="3">
-        <v>300</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
       </c>
       <c r="L44" s="3">
+        <v>300</v>
+      </c>
+      <c r="M44" s="3">
         <v>200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>300</v>
       </c>
       <c r="N44" s="3">
         <v>300</v>
       </c>
       <c r="O44" s="3">
+        <v>300</v>
+      </c>
+      <c r="P44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22800</v>
+        <v>24800</v>
       </c>
       <c r="E45" s="3">
-        <v>18300</v>
+        <v>21500</v>
       </c>
       <c r="F45" s="3">
-        <v>8700</v>
+        <v>18100</v>
       </c>
       <c r="G45" s="3">
-        <v>7000</v>
+        <v>7900</v>
       </c>
       <c r="H45" s="3">
-        <v>300</v>
-      </c>
-      <c r="I45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E46" s="3">
         <v>153700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>92200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>112900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>46700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>46300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>46400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>8800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>4900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2176,37 +2284,40 @@
         <v>12000</v>
       </c>
       <c r="F48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G48" s="3">
         <v>14200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4600</v>
       </c>
       <c r="M48" s="3">
         <v>4600</v>
       </c>
       <c r="N48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O48" s="3">
         <v>2300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2217,37 +2328,40 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>4600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,19 +2445,22 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -2349,13 +2469,13 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E54" s="3">
         <v>165800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>178100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>90700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>72300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,34 +2615,35 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E57" s="3">
         <v>28700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>48800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1000</v>
       </c>
       <c r="L57" s="3">
         <v>1000</v>
@@ -2521,42 +2652,45 @@
         <v>1000</v>
       </c>
       <c r="N57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
-        <v>6500</v>
-      </c>
       <c r="G58" s="3">
-        <v>3100</v>
+        <v>6900</v>
       </c>
       <c r="H58" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>4200</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>300</v>
@@ -2567,113 +2701,122 @@
       <c r="O58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>105200</v>
+        <v>96900</v>
       </c>
       <c r="E59" s="3">
-        <v>52900</v>
+        <v>103300</v>
       </c>
       <c r="F59" s="3">
-        <v>49200</v>
+        <v>52000</v>
       </c>
       <c r="G59" s="3">
+        <v>47500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E60" s="3">
         <v>137600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>79000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>104600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="H61" s="3">
-        <v>700</v>
+        <v>2100</v>
       </c>
       <c r="I61" s="3">
-        <v>700</v>
+        <v>2400</v>
       </c>
       <c r="J61" s="3">
-        <v>800</v>
+        <v>2500</v>
       </c>
       <c r="K61" s="3">
         <v>800</v>
@@ -2682,39 +2825,42 @@
         <v>800</v>
       </c>
       <c r="M61" s="3">
+        <v>800</v>
+      </c>
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>46300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>48600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3300</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>3300</v>
@@ -2723,16 +2869,19 @@
         <v>3300</v>
       </c>
       <c r="M62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N62" s="3">
         <v>3400</v>
-      </c>
-      <c r="N62" s="3">
-        <v>1100</v>
       </c>
       <c r="O62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>141100</v>
+        <v>140200</v>
       </c>
       <c r="E66" s="3">
-        <v>128700</v>
+        <v>137700</v>
       </c>
       <c r="F66" s="3">
-        <v>157300</v>
+        <v>125400</v>
       </c>
       <c r="G66" s="3">
-        <v>68900</v>
+        <v>153800</v>
       </c>
       <c r="H66" s="3">
+        <v>65300</v>
+      </c>
+      <c r="I66" s="3">
         <v>49200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-85100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-87400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-87200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-85400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-80200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-80400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-77000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-75100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-71400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E76" s="3">
         <v>24700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5300</v>
-      </c>
       <c r="H81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,31 +3624,32 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3461,14 +3660,17 @@
       <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
+      <c r="N83" s="3">
+        <v>500</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>8400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3742,37 +3963,40 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-4900</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,31 +4318,34 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
@@ -4108,39 +4354,42 @@
         <v>-100</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1800</v>
       </c>
       <c r="K102" s="3">
         <v>-1800</v>
       </c>
       <c r="L102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,212 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>201700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>175000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>107900</v>
       </c>
-      <c r="G8" s="3">
-        <v>171200</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>182200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>213000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>153000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2800</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2900</v>
       </c>
       <c r="N8" s="3">
         <v>2900</v>
       </c>
       <c r="O8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P8" s="3">
         <v>3000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>199300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>172500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>108300</v>
       </c>
-      <c r="G9" s="3">
-        <v>170700</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>179300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>157200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>208300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>148200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3100</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2500</v>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E10" s="3">
         <v>2500</v>
       </c>
       <c r="F10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="3">
         <v>-300</v>
       </c>
-      <c r="G10" s="3">
-        <v>500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,78 +982,84 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>400</v>
       </c>
       <c r="J15" s="3">
+        <v>400</v>
+      </c>
+      <c r="K15" s="3">
         <v>600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1049,13 +1071,16 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>205300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>177000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>111500</v>
       </c>
-      <c r="G17" s="3">
-        <v>175000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>184400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>160700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>214500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>155400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1800</v>
       </c>
       <c r="M18" s="3">
         <v>-1800</v>
       </c>
       <c r="N18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,122 +1207,129 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-3700</v>
       </c>
       <c r="F20" s="3">
         <v>-3700</v>
       </c>
       <c r="G20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H21" s="3">
+        <v>300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>1700</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1304,60 +1343,66 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>200</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1368,8 +1413,8 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>200</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1900</v>
       </c>
-      <c r="M26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>6400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3700</v>
       </c>
       <c r="F32" s="3">
         <v>3700</v>
       </c>
       <c r="G32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2049,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,184 +2141,199 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E43" s="3">
         <v>131900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70300</v>
       </c>
-      <c r="G43" s="3">
-        <v>100300</v>
-      </c>
       <c r="H43" s="3">
+        <v>53100</v>
+      </c>
+      <c r="I43" s="3">
         <v>61200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>300</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
       <c r="M44" s="3">
+        <v>300</v>
+      </c>
+      <c r="N44" s="3">
         <v>200</v>
-      </c>
-      <c r="N44" s="3">
-        <v>300</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
       <c r="P44" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E45" s="3">
         <v>24800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18100</v>
       </c>
-      <c r="G45" s="3">
-        <v>7900</v>
-      </c>
       <c r="H45" s="3">
+        <v>55100</v>
+      </c>
+      <c r="I45" s="3">
         <v>6400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E46" s="3">
         <v>159000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>153700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>112900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>70900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2254,26 +2358,29 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>4900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2287,37 +2394,40 @@
         <v>12000</v>
       </c>
       <c r="G48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H48" s="3">
         <v>14200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4600</v>
       </c>
       <c r="N48" s="3">
         <v>4600</v>
       </c>
       <c r="O48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2331,37 +2441,40 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>4600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2564,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2459,26 +2578,26 @@
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3">
+        <v>46400</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>5100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>164700</v>
+      </c>
+      <c r="E54" s="3">
         <v>171000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>165800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>150500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>178100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>90700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,37 +2745,38 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E57" s="3">
         <v>39900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>48800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1000</v>
       </c>
       <c r="M57" s="3">
         <v>1000</v>
@@ -2655,45 +2785,48 @@
         <v>1000</v>
       </c>
       <c r="O57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>200</v>
       </c>
       <c r="M58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
@@ -2704,96 +2837,105 @@
       <c r="P58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E59" s="3">
         <v>96900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>103300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
       </c>
       <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>5300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E60" s="3">
         <v>140100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>137600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>79000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>104600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2804,22 +2946,22 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>800</v>
       </c>
       <c r="L61" s="3">
         <v>800</v>
@@ -2828,16 +2970,19 @@
         <v>800</v>
       </c>
       <c r="N61" s="3">
+        <v>800</v>
+      </c>
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2853,8 +2998,8 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
+      <c r="H62" s="3">
+        <v>46000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -2862,8 +3007,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>3300</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>3300</v>
@@ -2872,16 +3017,19 @@
         <v>3300</v>
       </c>
       <c r="N62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O62" s="3">
         <v>3400</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1100</v>
       </c>
       <c r="P62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E66" s="3">
         <v>140200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>137700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>125400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>153800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-83900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-85100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-87400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-87200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-85400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-80200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-75100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-73300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-71400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E76" s="3">
         <v>27600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,34 +3822,35 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
@@ -3663,14 +3861,17 @@
       <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
+      <c r="O83" s="3">
+        <v>500</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>-4500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,13 +4170,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3966,37 +4186,40 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-12200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
-        <v>200</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-200</v>
       </c>
       <c r="M94" s="3">
         <v>-200</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,34 +4563,37 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
@@ -4357,16 +4602,19 @@
         <v>-100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,8 +4639,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1100</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1800</v>
       </c>
       <c r="L102" s="3">
         <v>-1800</v>
       </c>
       <c r="M102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,224 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
         <v>201700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>175000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107900</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>182200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>213000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>153000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2800</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2900</v>
       </c>
       <c r="O8" s="3">
         <v>2900</v>
       </c>
       <c r="P8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q8" s="3">
         <v>3000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
         <v>199300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>172500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>108300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>179300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>157200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>208300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>148200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3100</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2500</v>
+      <c r="D10" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="3">
         <v>2500</v>
       </c>
       <c r="G10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H10" s="3">
         <v>-300</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -996,73 +1016,76 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
       </c>
       <c r="K15" s="3">
+        <v>400</v>
+      </c>
+      <c r="L15" s="3">
         <v>600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>500</v>
@@ -1074,13 +1097,16 @@
         <v>500</v>
       </c>
       <c r="P15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3">
         <v>205300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>177000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>111500</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>184400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>160700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>214500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1800</v>
       </c>
       <c r="N18" s="3">
         <v>-1800</v>
       </c>
       <c r="O18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P18" s="3">
         <v>-1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,131 +1241,138 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-3700</v>
       </c>
       <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>1700</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1346,66 +1386,72 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1413,11 +1459,11 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
         <v>-5300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3">
+        <v>900</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,13 +1689,16 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>6400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3700</v>
       </c>
       <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="H32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
         <v>-5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
         <v>-5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,55 +2136,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2144,196 +2234,211 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E43" s="3">
         <v>25100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>70300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>35100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
       <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
-      </c>
-      <c r="O44" s="3">
-        <v>300</v>
       </c>
       <c r="P44" s="3">
         <v>300</v>
       </c>
       <c r="Q44" s="3">
+        <v>300</v>
+      </c>
+      <c r="R44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>123200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>55100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E46" s="3">
         <v>152700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>159000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>153700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>92200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>112900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>70900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2361,31 +2466,34 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>4900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="E48" s="3">
         <v>12000</v>
@@ -2397,37 +2505,40 @@
         <v>12000</v>
       </c>
       <c r="H48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I48" s="3">
         <v>14200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>4600</v>
       </c>
       <c r="O48" s="3">
         <v>4600</v>
       </c>
       <c r="P48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2444,37 +2555,40 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>4600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,13 +2684,16 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2581,26 +2701,26 @@
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>46400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E54" s="3">
         <v>164700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>171000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>165800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>150500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>178100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,40 +2876,41 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E57" s="3">
         <v>27000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>48800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>40500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1000</v>
       </c>
       <c r="N57" s="3">
         <v>1000</v>
@@ -2788,48 +2919,51 @@
         <v>1000</v>
       </c>
       <c r="P57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
       <c r="N58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -2840,107 +2974,116 @@
       <c r="Q58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E59" s="3">
         <v>96700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>96900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>103300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>300</v>
       </c>
       <c r="K59" s="3">
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>5300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E60" s="3">
         <v>132200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>140100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>137600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>79000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>104600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -2949,22 +3092,22 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>800</v>
       </c>
       <c r="M61" s="3">
         <v>800</v>
@@ -2973,21 +3116,24 @@
         <v>800</v>
       </c>
       <c r="O61" s="3">
+        <v>800</v>
+      </c>
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>100</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -2998,20 +3144,20 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>46000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>3300</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>3300</v>
@@ -3020,16 +3166,19 @@
         <v>3300</v>
       </c>
       <c r="O62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P62" s="3">
         <v>3400</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1100</v>
       </c>
       <c r="Q62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E66" s="3">
         <v>132300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>140200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>137700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>125400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>153800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-83200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-83900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-85100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-87400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-87200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-85400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-79400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-77000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-73300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E76" s="3">
         <v>29200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
         <v>-5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,37 +4021,38 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
         <v>200</v>
       </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -3864,14 +4063,17 @@
       <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
+      <c r="P83" s="3">
+        <v>500</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2600</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,16 +4391,17 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4188,38 +4409,41 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-12200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-200</v>
       </c>
       <c r="N94" s="3">
         <v>-200</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4407,8 +4641,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,37 +4809,40 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2800</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
@@ -4605,16 +4851,19 @@
         <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4642,8 +4891,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-9000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-1800</v>
       </c>
       <c r="M102" s="3">
         <v>-1800</v>
       </c>
       <c r="N102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E8" s="3">
         <v>132200</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>201700</v>
       </c>
-      <c r="G8" s="3">
-        <v>175000</v>
-      </c>
       <c r="H8" s="3">
-        <v>107900</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+        <v>173300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>106500</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>182200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>213000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>153000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2900</v>
       </c>
       <c r="P8" s="3">
         <v>2900</v>
       </c>
       <c r="Q8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R8" s="3">
         <v>3000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E9" s="3">
         <v>126200</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
         <v>199300</v>
       </c>
-      <c r="G9" s="3">
-        <v>172500</v>
-      </c>
       <c r="H9" s="3">
-        <v>108300</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+        <v>167500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>103700</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>179300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>157200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>208300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3100</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
       <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6000</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2500</v>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G10" s="3">
         <v>2500</v>
       </c>
       <c r="H10" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,13 +1022,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1019,44 +1039,47 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1064,31 +1087,31 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>400</v>
       </c>
       <c r="L15" s="3">
+        <v>400</v>
+      </c>
+      <c r="M15" s="3">
         <v>600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>500</v>
@@ -1100,13 +1123,16 @@
         <v>500</v>
       </c>
       <c r="Q15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>130700</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>129900</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
         <v>205300</v>
       </c>
-      <c r="G17" s="3">
-        <v>177000</v>
-      </c>
       <c r="H17" s="3">
-        <v>111500</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+        <v>170000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>105500</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>184400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>160700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>214500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>155400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1800</v>
       </c>
       <c r="O18" s="3">
         <v>-1800</v>
       </c>
       <c r="P18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,140 +1275,147 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-800</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-6400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3700</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2900</v>
       </c>
-      <c r="G21" s="3">
-        <v>1900</v>
-      </c>
       <c r="H21" s="3">
-        <v>500</v>
+        <v>3400</v>
       </c>
       <c r="I21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="3">
-        <v>500</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1389,61 +1429,67 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="H23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1453,8 +1499,8 @@
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1462,11 +1508,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2300</v>
       </c>
-      <c r="H26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="I26" s="3">
+        <v>800</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
         <v>900</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,17 +1750,20 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -1713,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>800</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>6400</v>
       </c>
-      <c r="G32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3700</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,208 +2327,223 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>47800</v>
+        <v>50200</v>
       </c>
       <c r="E43" s="3">
+        <v>54100</v>
+      </c>
+      <c r="F43" s="3">
         <v>25100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>131900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>118500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>61200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>35100</v>
-      </c>
-      <c r="M44" s="3">
-        <v>300</v>
       </c>
       <c r="N44" s="3">
         <v>300</v>
       </c>
       <c r="O44" s="3">
+        <v>300</v>
+      </c>
+      <c r="P44" s="3">
         <v>200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>300</v>
       </c>
       <c r="Q44" s="3">
         <v>300</v>
       </c>
       <c r="R44" s="3">
+        <v>300</v>
+      </c>
+      <c r="S44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4900</v>
+        <v>66100</v>
       </c>
       <c r="E45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F45" s="3">
         <v>123200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
       </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E46" s="3">
         <v>71800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>152700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>159000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>153700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>112900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2469,34 +2574,37 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>4900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="E48" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="F48" s="3">
         <v>12000</v>
@@ -2508,37 +2616,40 @@
         <v>12000</v>
       </c>
       <c r="I48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J48" s="3">
         <v>14200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>4600</v>
       </c>
       <c r="P48" s="3">
         <v>4600</v>
       </c>
       <c r="Q48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="R48" s="3">
         <v>2300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2558,37 +2669,40 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>4600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,43 +2804,46 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
+        <v>46400</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
-        <v>46400</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>8900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E54" s="3">
         <v>83700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>164700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>171000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>165800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>178100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>72300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,43 +3007,44 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>36700</v>
+        <v>33000</v>
       </c>
       <c r="E57" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F57" s="3">
         <v>27000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>57000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>40500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1000</v>
       </c>
       <c r="O57" s="3">
         <v>1000</v>
@@ -2922,51 +3053,54 @@
         <v>1000</v>
       </c>
       <c r="Q57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E58" s="3">
         <v>10900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>300</v>
@@ -2977,113 +3111,122 @@
       <c r="R58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>96700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>96900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>103300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>300</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
       <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>5300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E60" s="3">
         <v>49900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>132200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>140100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>137600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>104600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -3095,22 +3238,22 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>800</v>
       </c>
       <c r="N61" s="3">
         <v>800</v>
@@ -3119,21 +3262,24 @@
         <v>800</v>
       </c>
       <c r="P61" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -3147,20 +3293,20 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>46000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>3300</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>3300</v>
@@ -3169,16 +3315,19 @@
         <v>3300</v>
       </c>
       <c r="P62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q62" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1100</v>
       </c>
       <c r="R62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E66" s="3">
         <v>50000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>132300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>140200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>137700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>125400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>153800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-81900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-82200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-83200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-83900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-85100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-87400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-87200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-85400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-80400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-79400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-75100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-71400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E76" s="3">
         <v>30600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,40 +4220,41 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
@@ -4066,14 +4265,17 @@
       <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
+      <c r="Q83" s="3">
+        <v>500</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="G89" s="3">
-        <v>8400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4403,47 +4624,50 @@
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-4800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4644,8 +4878,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,40 +5055,43 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2800</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
@@ -4854,24 +5100,27 @@
         <v>-100</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>8</v>
@@ -4894,8 +5143,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-9000</v>
       </c>
-      <c r="G102" s="3">
-        <v>8700</v>
-      </c>
       <c r="H102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-1800</v>
       </c>
       <c r="N102" s="3">
         <v>-1800</v>
       </c>
       <c r="O102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>SDOT</t>
   </si>
@@ -656,263 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>114400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>132200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>220200</v>
+      </c>
+      <c r="J8" s="3">
         <v>200900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>173300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>106500</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>182200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>160300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>213000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>153000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>109400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>126200</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>213700</v>
+      </c>
+      <c r="J9" s="3">
         <v>193200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>167500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>103700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>179300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>157200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>208300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>148200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F10" s="3">
         <v>-6300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>6000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J10" s="3">
         <v>7700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +958,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,23 +1078,29 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>500</v>
       </c>
       <c r="E14" s="3">
+        <v>47900</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1074,35 +1113,41 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1116,34 +1161,34 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>500</v>
-      </c>
-      <c r="P15" s="3">
-        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>500</v>
@@ -1152,13 +1197,19 @@
         <v>500</v>
       </c>
       <c r="S15" s="3">
+        <v>500</v>
+      </c>
+      <c r="T15" s="3">
+        <v>500</v>
+      </c>
+      <c r="U15" s="3">
         <v>400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1227,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F17" s="3">
         <v>14600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>112600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>129900</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>217700</v>
+      </c>
+      <c r="J17" s="3">
         <v>197400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>170000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>105500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>184400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>160700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>214500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>155400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2300</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J18" s="3">
         <v>3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1375,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1339,132 +1406,144 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-14300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2300</v>
       </c>
-      <c r="G21" s="3">
-        <v>100</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J21" s="3">
         <v>3500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-1300</v>
       </c>
       <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1475,84 +1554,96 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-79300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-15200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1800</v>
       </c>
       <c r="R23" s="3">
         <v>-1900</v>
       </c>
       <c r="S23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1560,14 +1651,14 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>8</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1590,8 +1681,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-79100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-15200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>800</v>
+      </c>
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>-5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-1800</v>
       </c>
       <c r="R26" s="3">
         <v>-1900</v>
       </c>
       <c r="S26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-15200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>700</v>
+      </c>
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1800</v>
       </c>
       <c r="R27" s="3">
         <v>-1900</v>
       </c>
       <c r="S27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1823,29 +1944,29 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>100</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J29" s="3">
         <v>-700</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2115,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2011,91 +2150,103 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-15200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>700</v>
+      </c>
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1800</v>
       </c>
       <c r="R33" s="3">
         <v>-1900</v>
       </c>
       <c r="S33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-15200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>700</v>
+      </c>
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1800</v>
       </c>
       <c r="R35" s="3">
         <v>-1900</v>
       </c>
       <c r="S35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2482,72 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>13500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>14800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>15800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,244 +2602,274 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>31500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>50200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>54100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>25100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>131900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>118500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>70300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>53100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>61200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>47500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>300</v>
-      </c>
-      <c r="N44" s="3">
-        <v>35100</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
       <c r="P44" s="3">
+        <v>35100</v>
+      </c>
+      <c r="Q44" s="3">
         <v>300</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>200</v>
       </c>
       <c r="R44" s="3">
         <v>300</v>
       </c>
       <c r="S44" s="3">
+        <v>200</v>
+      </c>
+      <c r="T44" s="3">
         <v>300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
+        <v>300</v>
+      </c>
+      <c r="V44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>13700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>66100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>123200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>24800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>21500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>18100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>55100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F46" s="3">
         <v>47700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>118700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>71800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>152700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>159000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>153700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>92200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>112900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>70900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>53200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>46700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>14600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>16500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>18000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>13400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2685,43 +2894,49 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>4900</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>11900</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>11900</v>
       </c>
       <c r="G48" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="H48" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="I48" s="3">
         <v>12000</v>
@@ -2730,37 +2945,43 @@
         <v>12000</v>
       </c>
       <c r="K48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="M48" s="3">
         <v>14200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2786,37 +3007,43 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>4600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>7200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>9000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2950,29 +3189,29 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>46400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -2983,8 +3222,14 @@
       <c r="T52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3284,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F54" s="3">
         <v>73000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>130600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>83700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>164700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>171000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>165800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>150500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>178100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>90700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>72300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>62600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>27700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>29900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>29400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,111 +3398,119 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F57" s="3">
         <v>33700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>33000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>32700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>27000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>39900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>28700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>48800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>57000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>40500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>35500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1000</v>
       </c>
       <c r="R57" s="3">
         <v>1000</v>
       </c>
       <c r="S57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F58" s="3">
         <v>11600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>300</v>
       </c>
       <c r="S58" s="3">
         <v>300</v>
@@ -3251,134 +3518,152 @@
       <c r="T58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>300</v>
+      </c>
+      <c r="V58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>48800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>96700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>96900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>103300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>52000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>47500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>57600</v>
+      </c>
+      <c r="F60" s="3">
         <v>49100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>94500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>49900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>132200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>140100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>137600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>79000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>104600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>61900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>45500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>40300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -3387,45 +3672,51 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>800</v>
-      </c>
-      <c r="P61" s="3">
-        <v>800</v>
       </c>
       <c r="Q61" s="3">
         <v>800</v>
       </c>
       <c r="R61" s="3">
+        <v>800</v>
+      </c>
+      <c r="S61" s="3">
+        <v>800</v>
+      </c>
+      <c r="T61" s="3">
         <v>900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>700</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -3445,38 +3736,44 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>46000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3300</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>3300</v>
       </c>
       <c r="R62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T62" s="3">
         <v>3400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3952,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>57600</v>
+      </c>
+      <c r="F66" s="3">
         <v>49300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>94700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>50000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>132300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>140200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>137700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>125400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>153800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>65300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>49200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>44000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,13 +4162,19 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4286,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-181500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-176600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-97100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-81900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-82200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-83200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-83900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-85100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-87400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-87200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-85400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-80200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-80400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-79400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-75100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-73300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-71400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4534,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="F76" s="3">
         <v>20700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>33000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>30600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>29200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>27600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>24700</v>
-      </c>
-      <c r="J76" s="3">
-        <v>21800</v>
-      </c>
-      <c r="K76" s="3">
-        <v>20800</v>
       </c>
       <c r="L76" s="3">
         <v>21800</v>
       </c>
       <c r="M76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="N76" s="3">
+        <v>21800</v>
+      </c>
+      <c r="O76" s="3">
         <v>23200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>18600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>16600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>18900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>24400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-15200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>700</v>
+      </c>
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1800</v>
       </c>
       <c r="R81" s="3">
         <v>-1900</v>
       </c>
       <c r="S81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,16 +4815,18 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4438,19 +4835,19 @@
         <v>8</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -4459,10 +4856,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
@@ -4470,14 +4867,20 @@
       <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
+        <v>500</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-3000</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-9800</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5273,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4851,38 +5292,38 @@
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-12200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-200</v>
@@ -4890,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,8 +5455,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5013,53 +5472,59 @@
       <c r="E94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-4900</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5118,11 +5585,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,72 +5789,84 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F100" s="3">
         <v>2200</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-100</v>
-      </c>
       <c r="P100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -5377,8 +5874,8 @@
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
@@ -5398,11 +5895,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5416,16 +5913,22 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>200</v>
@@ -5434,42 +5937,48 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>800</v>
+      </c>
+      <c r="J102" s="3">
         <v>-9000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T102" s="3" t="s">
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
